--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260824.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260824.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.72%</t>
+          <t>9.51%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.32%</t>
+          <t>9.42%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.10%</t>
+          <t>6.00%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.86%</t>
+          <t>5.87%</t>
         </is>
       </c>
     </row>
@@ -704,51 +704,51 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>4.48%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>602,716,270</t>
+          <t>187,201,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.79%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>187,201,000</t>
+          <t>602,716,270</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.60%</t>
         </is>
       </c>
     </row>
@@ -792,134 +792,134 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>456,296,250</t>
+          <t>64,092,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>131,951,945</t>
+          <t>456,296,250</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>360,120,964</t>
+          <t>131,951,945</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>64,092,000</t>
+          <t>31,356,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>31,356,000</t>
+          <t>360,120,964</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>199,761,000</t>
+          <t>26,219,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,61 +931,61 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>26,219,000</t>
+          <t>199,761,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>236,458,056</t>
+          <t>131,081,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>131,081,000</t>
+          <t>1,683</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,88 +997,88 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>145,204,000</t>
+          <t>98,298,442</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>98,298,442</t>
+          <t>236,458,056</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>83,020,000</t>
+          <t>145,204,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,589</t>
+          <t>83,020,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,886,000</t>
+          <t>10,986,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>28,471,230,449</t>
+          <t>29,284,016,439</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,800,572,369</t>
+          <t>4,672,064,885</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-31,040,316</t>
+          <t>-19,409,360</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
